--- a/reports/2026-08_月次実績報告/excel/第51期下期広域営業部担当者別実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期下期広域営業部担当者別実績.xlsx
@@ -5379,7 +5379,7 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E9" s="4">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E10" s="4">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E22" s="4">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E23" s="4">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E35" s="4">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E36" s="4">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E48" s="4" t="n"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="D61" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E61" s="3">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E62" s="3">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E74" s="4">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E75" s="17">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="D87" s="155" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E87" s="3">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="D88" s="155" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E88" s="3">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E100" s="4">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="D101" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E101" s="4">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="D113" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E113" s="4">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E114" s="4">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E9" s="4" t="n"/>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E22" s="4" t="n"/>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E35" s="4">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E36" s="4">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E48" s="4" t="n"/>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="D61" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E61" s="3">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E62" s="3">
@@ -18542,7 +18542,7 @@
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E74" s="4">
@@ -18638,7 +18638,7 @@
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E75" s="17">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="D87" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E87" s="4" t="n"/>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E100" s="4">
@@ -20440,7 +20440,7 @@
       </c>
       <c r="D101" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E101" s="4">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="D113" s="20" t="inlineStr">
         <is>
-          <t>馬場部長</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E113" s="4">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E114" s="4">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="D9" s="76" t="inlineStr">
         <is>
-          <t>馬場部長（東京）</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -23082,7 +23082,7 @@
       </c>
       <c r="D22" s="76" t="inlineStr">
         <is>
-          <t>馬場部長（東京）</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
@@ -23166,7 +23166,7 @@
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -24025,7 +24025,7 @@
       </c>
       <c r="D35" s="76" t="inlineStr">
         <is>
-          <t>馬場部長（東京）</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E35" s="4">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E36" s="4">
@@ -25009,7 +25009,7 @@
       </c>
       <c r="D48" s="76" t="inlineStr">
         <is>
-          <t>馬場部長（東京）</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E48" s="4">
@@ -25105,7 +25105,7 @@
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E49" s="4">
@@ -26039,7 +26039,7 @@
       </c>
       <c r="D61" s="76" t="inlineStr">
         <is>
-          <t>馬場部長（東京）</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E61" s="3">
@@ -26135,7 +26135,7 @@
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E62" s="3">
@@ -27019,7 +27019,7 @@
       </c>
       <c r="D74" s="76" t="inlineStr">
         <is>
-          <t>馬場部長（東京）</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E74" s="4">
@@ -27115,7 +27115,7 @@
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E75" s="4">
@@ -27928,7 +27928,7 @@
       </c>
       <c r="D87" s="76" t="inlineStr">
         <is>
-          <t>馬場部長（東京）</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -28863,7 +28863,7 @@
       </c>
       <c r="D100" s="76" t="inlineStr">
         <is>
-          <t>馬場部長（東京）</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E100" s="4">
@@ -28953,7 +28953,7 @@
       </c>
       <c r="D101" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E101" s="4">
@@ -29828,7 +29828,7 @@
       </c>
       <c r="D113" s="76" t="inlineStr">
         <is>
-          <t>馬場部長（東京）</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E113" s="4">
@@ -29918,7 +29918,7 @@
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E114" s="4">

--- a/reports/2026-08_月次実績報告/excel/第51期下期広域営業部担当者別実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期下期広域営業部担当者別実績.xlsx
@@ -19684,7 +19684,9 @@
       <c r="H90" s="59" t="n">
         <v>46.2</v>
       </c>
-      <c r="I90" s="59" t="n"/>
+      <c r="I90" s="59" t="n">
+        <v>286.455</v>
+      </c>
       <c r="J90" s="59" t="n"/>
       <c r="K90" s="72">
         <f>SUM(E90:J90)</f>
@@ -19702,7 +19704,9 @@
       <c r="O90" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="P90" s="59" t="n"/>
+      <c r="P90" s="59" t="n">
+        <v>25.625</v>
+      </c>
       <c r="Q90" s="59" t="n"/>
       <c r="R90" s="72">
         <f>SUM(L90:Q90)</f>

--- a/reports/2026-08_月次実績報告/excel/第51期下期広域営業部担当者別実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期下期広域営業部担当者別実績.xlsx
@@ -19684,9 +19684,7 @@
       <c r="H90" s="59" t="n">
         <v>46.2</v>
       </c>
-      <c r="I90" s="59" t="n">
-        <v>286.455</v>
-      </c>
+      <c r="I90" s="59" t="n"/>
       <c r="J90" s="59" t="n"/>
       <c r="K90" s="72">
         <f>SUM(E90:J90)</f>
@@ -19704,9 +19702,7 @@
       <c r="O90" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="P90" s="59" t="n">
-        <v>25.625</v>
-      </c>
+      <c r="P90" s="59" t="n"/>
       <c r="Q90" s="59" t="n"/>
       <c r="R90" s="72">
         <f>SUM(L90:Q90)</f>

--- a/reports/2026-08_月次実績報告/excel/第51期下期広域営業部担当者別実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期下期広域営業部担当者別実績.xlsx
@@ -28048,7 +28048,7 @@
         <v>930.6950000000001</v>
       </c>
       <c r="P88" s="4" t="n">
-        <v>715.4935</v>
+        <v>712.8835</v>
       </c>
       <c r="Q88" s="4" t="n"/>
       <c r="R88" s="84">
